--- a/ig/nr-add-sato2-profile/StructureDefinition-mesures-observation-pain-severity.xlsx
+++ b/ig/nr-add-sato2-profile/StructureDefinition-mesures-observation-pain-severity.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3956" uniqueCount="658">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3956" uniqueCount="659">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-17T15:33:27+00:00</t>
+    <t>2023-11-17T15:40:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -444,6 +444,9 @@
   </si>
   <si>
     <t>Uri identifiant les systèmes tiers ayant envoyé la ressource. L’uri est sous la forme d’une oid : « urn:oid:xx.xx.xx »</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -3434,10 +3437,10 @@
         <v>137</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3487,7 +3490,7 @@
         <v>81</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>79</v>
@@ -3522,10 +3525,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -3548,16 +3551,16 @@
         <v>93</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -3607,7 +3610,7 @@
         <v>81</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>79</v>
@@ -3642,10 +3645,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3668,16 +3671,16 @@
         <v>93</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3703,13 +3706,13 @@
         <v>81</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>81</v>
@@ -3727,7 +3730,7 @@
         <v>81</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -3748,10 +3751,10 @@
         <v>81</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>81</v>
@@ -3762,10 +3765,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3788,16 +3791,16 @@
         <v>93</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3823,13 +3826,13 @@
         <v>81</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>81</v>
@@ -3847,7 +3850,7 @@
         <v>81</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -3868,10 +3871,10 @@
         <v>81</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>81</v>
@@ -3882,10 +3885,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3911,13 +3914,13 @@
         <v>136</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3967,7 +3970,7 @@
         <v>81</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -4002,10 +4005,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4028,16 +4031,16 @@
         <v>81</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4063,13 +4066,13 @@
         <v>81</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>81</v>
@@ -4087,7 +4090,7 @@
         <v>81</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -4122,14 +4125,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -4148,16 +4151,16 @@
         <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4207,7 +4210,7 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -4231,7 +4234,7 @@
         <v>81</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>81</v>
@@ -4242,14 +4245,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4268,16 +4271,16 @@
         <v>81</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4327,7 +4330,7 @@
         <v>81</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -4362,10 +4365,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4394,7 +4397,7 @@
         <v>116</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N17" t="s" s="2">
         <v>118</v>
@@ -4447,7 +4450,7 @@
         <v>121</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -4482,13 +4485,13 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>81</v>
@@ -4510,13 +4513,13 @@
         <v>81</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4567,7 +4570,7 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -4602,13 +4605,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>81</v>
@@ -4630,13 +4633,13 @@
         <v>81</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4687,7 +4690,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4722,10 +4725,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4751,16 +4754,16 @@
         <v>115</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>118</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>81</v>
@@ -4809,7 +4812,7 @@
         <v>121</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -4844,10 +4847,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4870,17 +4873,17 @@
         <v>93</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>81</v>
@@ -4929,7 +4932,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4944,19 +4947,19 @@
         <v>105</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>81</v>
@@ -4964,14 +4967,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4990,19 +4993,19 @@
         <v>93</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>81</v>
@@ -5051,7 +5054,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -5063,19 +5066,19 @@
         <v>104</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>81</v>
@@ -5086,14 +5089,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5112,16 +5115,16 @@
         <v>93</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5171,7 +5174,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -5183,19 +5186,19 @@
         <v>104</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>81</v>
@@ -5206,10 +5209,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5232,19 +5235,19 @@
         <v>93</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>81</v>
@@ -5269,13 +5272,13 @@
         <v>81</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>81</v>
@@ -5293,7 +5296,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>92</v>
@@ -5308,19 +5311,19 @@
         <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>81</v>
@@ -5328,10 +5331,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5354,19 +5357,19 @@
         <v>81</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>81</v>
@@ -5391,19 +5394,19 @@
         <v>81</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AC25" s="2"/>
       <c r="AD25" t="s" s="2">
@@ -5413,7 +5416,7 @@
         <v>121</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -5434,13 +5437,13 @@
         <v>81</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>81</v>
@@ -5448,13 +5451,13 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>81</v>
@@ -5476,19 +5479,19 @@
         <v>81</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>81</v>
@@ -5513,13 +5516,13 @@
         <v>81</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>81</v>
@@ -5537,7 +5540,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -5558,13 +5561,13 @@
         <v>81</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>81</v>
@@ -5572,10 +5575,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5690,10 +5693,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5810,10 +5813,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5836,19 +5839,19 @@
         <v>93</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>81</v>
@@ -5897,7 +5900,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5918,10 +5921,10 @@
         <v>81</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>81</v>
@@ -5932,10 +5935,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6050,10 +6053,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6170,10 +6173,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6199,23 +6202,23 @@
         <v>136</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>81</v>
@@ -6257,7 +6260,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -6278,10 +6281,10 @@
         <v>81</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>81</v>
@@ -6292,10 +6295,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6321,13 +6324,13 @@
         <v>108</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6377,7 +6380,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -6398,10 +6401,10 @@
         <v>81</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>81</v>
@@ -6412,10 +6415,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6438,26 +6441,26 @@
         <v>93</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>81</v>
@@ -6499,7 +6502,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -6520,10 +6523,10 @@
         <v>81</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>81</v>
@@ -6534,10 +6537,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6563,16 +6566,16 @@
         <v>108</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>81</v>
@@ -6582,7 +6585,7 @@
         <v>81</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="T35" t="s" s="2">
         <v>81</v>
@@ -6621,7 +6624,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6642,10 +6645,10 @@
         <v>81</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>81</v>
@@ -6656,10 +6659,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6682,19 +6685,19 @@
         <v>93</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -6743,7 +6746,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6764,10 +6767,10 @@
         <v>81</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>81</v>
@@ -6778,10 +6781,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6807,16 +6810,16 @@
         <v>108</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>81</v>
@@ -6865,7 +6868,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6886,10 +6889,10 @@
         <v>81</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>81</v>
@@ -6900,14 +6903,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6926,19 +6929,19 @@
         <v>93</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>81</v>
@@ -6948,7 +6951,7 @@
         <v>81</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>81</v>
@@ -6963,13 +6966,13 @@
         <v>81</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>81</v>
@@ -6987,7 +6990,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>92</v>
@@ -7002,30 +7005,30 @@
         <v>105</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7048,19 +7051,19 @@
         <v>93</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>81</v>
@@ -7109,7 +7112,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -7121,22 +7124,22 @@
         <v>104</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>81</v>
@@ -7144,10 +7147,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7170,16 +7173,16 @@
         <v>93</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7229,7 +7232,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -7241,7 +7244,7 @@
         <v>104</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>81</v>
@@ -7250,13 +7253,13 @@
         <v>81</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>81</v>
@@ -7264,14 +7267,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7290,19 +7293,19 @@
         <v>93</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>81</v>
@@ -7351,7 +7354,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -7363,22 +7366,22 @@
         <v>104</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>81</v>
@@ -7386,14 +7389,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -7412,19 +7415,19 @@
         <v>93</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>81</v>
@@ -7473,7 +7476,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7482,25 +7485,25 @@
         <v>92</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>81</v>
@@ -7508,10 +7511,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7537,13 +7540,13 @@
         <v>130</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7593,7 +7596,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7614,13 +7617,13 @@
         <v>81</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>81</v>
@@ -7628,10 +7631,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7654,19 +7657,19 @@
         <v>93</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -7715,7 +7718,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7727,22 +7730,22 @@
         <v>104</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>81</v>
@@ -7750,10 +7753,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7776,19 +7779,19 @@
         <v>93</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
@@ -7837,7 +7840,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7846,7 +7849,7 @@
         <v>92</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>105</v>
@@ -7855,27 +7858,27 @@
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7990,10 +7993,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8110,10 +8113,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8136,19 +8139,19 @@
         <v>93</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -8197,7 +8200,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -8218,10 +8221,10 @@
         <v>81</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>81</v>
@@ -8232,10 +8235,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8258,25 +8261,25 @@
         <v>93</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q49" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="R49" t="s" s="2">
         <v>81</v>
@@ -8297,13 +8300,13 @@
         <v>81</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>81</v>
@@ -8321,7 +8324,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -8342,10 +8345,10 @@
         <v>81</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>81</v>
@@ -8356,10 +8359,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8385,16 +8388,16 @@
         <v>108</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>81</v>
@@ -8404,7 +8407,7 @@
         <v>81</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>81</v>
@@ -8443,7 +8446,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -8464,10 +8467,10 @@
         <v>81</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>81</v>
@@ -8478,10 +8481,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8507,16 +8510,16 @@
         <v>136</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>81</v>
@@ -8526,7 +8529,7 @@
         <v>81</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>81</v>
@@ -8565,7 +8568,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8574,7 +8577,7 @@
         <v>92</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>105</v>
@@ -8586,10 +8589,10 @@
         <v>81</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>81</v>
@@ -8600,10 +8603,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8626,19 +8629,19 @@
         <v>93</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>81</v>
@@ -8687,7 +8690,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8708,10 +8711,10 @@
         <v>81</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>81</v>
@@ -8722,10 +8725,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8748,19 +8751,19 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>81</v>
@@ -8785,13 +8788,13 @@
         <v>81</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>81</v>
@@ -8809,7 +8812,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8818,7 +8821,7 @@
         <v>92</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>105</v>
@@ -8833,7 +8836,7 @@
         <v>106</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>81</v>
@@ -8844,10 +8847,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8962,10 +8965,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9082,10 +9085,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9108,19 +9111,19 @@
         <v>93</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -9169,7 +9172,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -9190,10 +9193,10 @@
         <v>81</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>81</v>
@@ -9204,10 +9207,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9322,10 +9325,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9442,10 +9445,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9471,16 +9474,16 @@
         <v>136</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>81</v>
@@ -9529,7 +9532,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9550,10 +9553,10 @@
         <v>81</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>81</v>
@@ -9564,10 +9567,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9593,13 +9596,13 @@
         <v>108</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9649,7 +9652,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9670,10 +9673,10 @@
         <v>81</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>81</v>
@@ -9684,10 +9687,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9710,19 +9713,19 @@
         <v>93</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>81</v>
@@ -9771,7 +9774,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9792,10 +9795,10 @@
         <v>81</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>81</v>
@@ -9806,10 +9809,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9835,16 +9838,16 @@
         <v>108</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>81</v>
@@ -9893,7 +9896,7 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9914,10 +9917,10 @@
         <v>81</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>81</v>
@@ -9928,10 +9931,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9954,19 +9957,19 @@
         <v>93</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>81</v>
@@ -10015,7 +10018,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -10036,10 +10039,10 @@
         <v>81</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>81</v>
@@ -10050,10 +10053,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10079,16 +10082,16 @@
         <v>108</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>81</v>
@@ -10137,7 +10140,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -10158,10 +10161,10 @@
         <v>81</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>81</v>
@@ -10172,14 +10175,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -10198,19 +10201,19 @@
         <v>81</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>81</v>
@@ -10235,13 +10238,13 @@
         <v>81</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>81</v>
@@ -10259,7 +10262,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -10277,27 +10280,27 @@
         <v>81</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10320,19 +10323,19 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>81</v>
@@ -10381,7 +10384,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -10402,10 +10405,10 @@
         <v>81</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>81</v>
@@ -10416,10 +10419,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10442,16 +10445,16 @@
         <v>81</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10477,13 +10480,13 @@
         <v>81</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>81</v>
@@ -10501,7 +10504,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10519,27 +10522,27 @@
         <v>81</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10562,19 +10565,19 @@
         <v>81</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>81</v>
@@ -10599,13 +10602,13 @@
         <v>81</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>81</v>
@@ -10623,7 +10626,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10644,10 +10647,10 @@
         <v>81</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>81</v>
@@ -10658,10 +10661,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10776,10 +10779,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10896,10 +10899,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10922,19 +10925,19 @@
         <v>93</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>81</v>
@@ -10983,7 +10986,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -11004,10 +11007,10 @@
         <v>81</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>81</v>
@@ -11018,10 +11021,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11136,10 +11139,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11256,10 +11259,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11285,16 +11288,16 @@
         <v>136</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>81</v>
@@ -11343,7 +11346,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -11364,10 +11367,10 @@
         <v>81</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>81</v>
@@ -11378,10 +11381,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11407,13 +11410,13 @@
         <v>108</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11463,7 +11466,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -11484,10 +11487,10 @@
         <v>81</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>81</v>
@@ -11498,10 +11501,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11524,19 +11527,19 @@
         <v>93</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>81</v>
@@ -11585,7 +11588,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -11606,10 +11609,10 @@
         <v>81</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>81</v>
@@ -11620,10 +11623,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11649,16 +11652,16 @@
         <v>108</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>81</v>
@@ -11707,7 +11710,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11728,10 +11731,10 @@
         <v>81</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>81</v>
@@ -11742,10 +11745,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11768,19 +11771,19 @@
         <v>93</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>81</v>
@@ -11829,7 +11832,7 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11850,10 +11853,10 @@
         <v>81</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>81</v>
@@ -11864,10 +11867,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11893,16 +11896,16 @@
         <v>108</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>81</v>
@@ -11951,7 +11954,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11972,10 +11975,10 @@
         <v>81</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>81</v>
@@ -11986,10 +11989,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12012,16 +12015,16 @@
         <v>81</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -12071,7 +12074,7 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -12083,33 +12086,33 @@
         <v>104</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12132,16 +12135,16 @@
         <v>81</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12191,7 +12194,7 @@
         <v>81</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -12203,33 +12206,33 @@
         <v>104</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12252,19 +12255,19 @@
         <v>81</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>81</v>
@@ -12313,7 +12316,7 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -12325,7 +12328,7 @@
         <v>104</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>81</v>
@@ -12334,10 +12337,10 @@
         <v>81</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>81</v>
@@ -12348,10 +12351,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12466,10 +12469,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12586,14 +12589,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12615,16 +12618,16 @@
         <v>115</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N85" t="s" s="2">
         <v>118</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>81</v>
@@ -12673,7 +12676,7 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -12708,10 +12711,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12734,16 +12737,16 @@
         <v>81</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12793,7 +12796,7 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12802,10 +12805,10 @@
         <v>92</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>81</v>
@@ -12814,10 +12817,10 @@
         <v>81</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>81</v>
@@ -12828,10 +12831,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12854,16 +12857,16 @@
         <v>81</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12913,7 +12916,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -12922,10 +12925,10 @@
         <v>92</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>81</v>
@@ -12934,10 +12937,10 @@
         <v>81</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>81</v>
@@ -12948,10 +12951,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12974,19 +12977,19 @@
         <v>81</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>81</v>
@@ -13011,13 +13014,13 @@
         <v>81</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>81</v>
@@ -13035,7 +13038,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -13053,13 +13056,13 @@
         <v>81</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>81</v>
@@ -13070,10 +13073,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13096,19 +13099,19 @@
         <v>81</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>81</v>
@@ -13133,13 +13136,13 @@
         <v>81</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>81</v>
@@ -13157,7 +13160,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -13175,13 +13178,13 @@
         <v>81</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>81</v>
@@ -13192,10 +13195,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13218,19 +13221,19 @@
         <v>81</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>81</v>
@@ -13279,7 +13282,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -13291,7 +13294,7 @@
         <v>104</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>81</v>
@@ -13300,10 +13303,10 @@
         <v>81</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>81</v>
@@ -13314,10 +13317,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13343,13 +13346,13 @@
         <v>108</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -13399,7 +13402,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -13420,10 +13423,10 @@
         <v>81</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>81</v>
@@ -13434,10 +13437,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13460,16 +13463,16 @@
         <v>93</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13519,7 +13522,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -13531,7 +13534,7 @@
         <v>104</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>81</v>
@@ -13540,10 +13543,10 @@
         <v>81</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>81</v>
@@ -13554,10 +13557,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13580,16 +13583,16 @@
         <v>93</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13639,7 +13642,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -13651,7 +13654,7 @@
         <v>104</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>81</v>
@@ -13660,10 +13663,10 @@
         <v>81</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>81</v>
@@ -13674,10 +13677,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13700,19 +13703,19 @@
         <v>93</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>81</v>
@@ -13761,7 +13764,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -13773,7 +13776,7 @@
         <v>104</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>81</v>
@@ -13782,10 +13785,10 @@
         <v>81</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>81</v>
@@ -13796,10 +13799,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13914,10 +13917,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14034,14 +14037,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -14063,16 +14066,16 @@
         <v>115</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>118</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>81</v>
@@ -14121,7 +14124,7 @@
         <v>81</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -14156,10 +14159,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14182,19 +14185,19 @@
         <v>93</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>81</v>
@@ -14219,13 +14222,13 @@
         <v>81</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>81</v>
@@ -14243,7 +14246,7 @@
         <v>81</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>92</v>
@@ -14261,16 +14264,16 @@
         <v>81</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AP98" t="s" s="2">
         <v>81</v>
@@ -14278,10 +14281,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14304,19 +14307,19 @@
         <v>93</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>81</v>
@@ -14341,13 +14344,13 @@
         <v>81</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>81</v>
@@ -14365,7 +14368,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -14374,7 +14377,7 @@
         <v>92</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>105</v>
@@ -14383,27 +14386,27 @@
         <v>81</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14426,19 +14429,19 @@
         <v>81</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>81</v>
@@ -14463,13 +14466,13 @@
         <v>81</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>81</v>
@@ -14487,7 +14490,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -14496,7 +14499,7 @@
         <v>92</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>105</v>
@@ -14511,7 +14514,7 @@
         <v>106</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>81</v>
@@ -14522,14 +14525,14 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -14548,19 +14551,19 @@
         <v>81</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>81</v>
@@ -14585,13 +14588,13 @@
         <v>81</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>81</v>
@@ -14609,7 +14612,7 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -14627,27 +14630,27 @@
         <v>81</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14673,16 +14676,16 @@
         <v>82</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>81</v>
@@ -14731,7 +14734,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -14752,10 +14755,10 @@
         <v>81</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>81</v>

--- a/ig/nr-add-sato2-profile/StructureDefinition-mesures-observation-pain-severity.xlsx
+++ b/ig/nr-add-sato2-profile/StructureDefinition-mesures-observation-pain-severity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-17T15:40:40+00:00</t>
+    <t>2023-11-23T10:07:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
